--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp7.280.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.514.000</t>
+          <t>Rp2.118.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp4.290.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.200.000</t>
+          <t>Rp20.800.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.985.000</t>
+          <t>Rp6.495.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.171.500</t>
+          <t>Rp11.776.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.095.000</t>
+          <t>Rp1.395.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.286.000</t>
+          <t>Rp2.466.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.458.000</t>
+          <t>Rp1.878.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp698.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.196.000</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.060.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.182.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.560.000</t>
+          <t>Rp6.320.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp497.000</t>
+          <t>Rp1.093.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp2.339.000</t>
+          <t>Rp2.439.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.720.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.085.000</t>
+          <t>Rp4.220.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3878,24 +3878,24 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp750.000</t>
+          <t>Rp125.000 - Rp700.000</t>
         </is>
       </c>
     </row>
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp10.250.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>60</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.479.000</t>
+          <t>Rp8.273.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.575.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp378.000</t>
+          <t>Rp716.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.850.000</t>
+          <t>Rp15.300.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp10.800.000</t>
+          <t>Rp12.000.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D64" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp8.700.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.273.000</t>
+          <t>Rp6.453.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D67" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.700.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp27.050.000</t>
+          <t>Rp27.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.165.000</t>
+          <t>Rp2.345.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.365.000</t>
+          <t>Rp15.755.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.057.000</t>
+          <t>Rp8.932.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.191.000</t>
+          <t>Rp18.401.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.915.000</t>
+          <t>Rp14.190.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.563.000</t>
+          <t>Rp4.703.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.150.000</t>
+          <t>Rp11.735.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp8.225.000</t>
+          <t>Rp10.225.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.580.000</t>
+          <t>Rp9.845.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp21.400.000</t>
+          <t>Rp23.400.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.890.000</t>
+          <t>Rp8.340.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.384.000</t>
+          <t>Rp4.932.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.495.000</t>
+          <t>Rp5.985.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.846.000</t>
+          <t>Rp5.572.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp420.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.690.000</t>
+          <t>Rp3.870.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.310.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.785.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.487.000</t>
+          <t>Rp2.787.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.524.983</t>
+          <t>Rp6.774.983</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.776.500</t>
+          <t>Rp10.264.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.395.000</t>
+          <t>Rp957.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp13.916.000</t>
+          <t>Rp14.115.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.466.000</t>
+          <t>Rp3.042.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp3.885.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.155.000</t>
+          <t>Rp5.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.890.000</t>
+          <t>Rp7.288.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.056.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp690.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp796.000</t>
+          <t>Rp1.294.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.687.500</t>
+          <t>Rp6.337.500</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.320.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>90</v>
       </c>
       <c r="D80" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.765.000</t>
+          <t>Rp4.468.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp810.000</t>
+          <t>Rp486.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.947.500</t>
+          <t>Rp14.130.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp574.000</t>
+          <t>Rp1.274.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp6.420.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp13.515.000</t>
+          <t>Rp13.790.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.198.000</t>
+          <t>Rp1.598.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.300.000</t>
+          <t>Rp17.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.125.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp53.000</t>
+          <t>Rp124.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp12.000.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D67" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp11.700.000</t>
+          <t>Rp12.100.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp27.550.000</t>
+          <t>Rp30.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.290.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.170.000</t>
+          <t>Rp5.470.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.780.000</t>
+          <t>Rp11.110.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.085.000</t>
+          <t>Rp12.360.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp536.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.190.000</t>
+          <t>Rp14.390.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp5.717.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.991.000</t>
+          <t>Rp6.639.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.040.000</t>
+          <t>Rp6.540.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp11.735.000</t>
+          <t>Rp12.665.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp10.225.000</t>
+          <t>Rp11.475.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.716.000</t>
+          <t>Rp2.092.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.210.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.985.000</t>
+          <t>Rp6.240.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp4.770.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.899.993</t>
+          <t>Rp3.299.991</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.130.000</t>
+          <t>Rp13.530.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.870.000</t>
+          <t>Rp4.260.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.429.000</t>
+          <t>Rp1.699.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp3.695.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.035.000</t>
+          <t>Rp2.185.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.220.000</t>
+          <t>Rp13.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.787.000</t>
+          <t>Rp3.537.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.338.000</t>
+          <t>Rp1.878.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp7.280.000</t>
+          <t>Rp7.040.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.774.983</t>
+          <t>Rp6.668.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.525.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.260.000</t>
+          <t>Rp9.510.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.264.000</t>
+          <t>Rp11.364.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp398.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.276.000</t>
+          <t>Rp2.424.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.640.000</t>
+          <t>Rp3.270.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.288.000</t>
+          <t>Rp8.688.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.592.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.144.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>36</v>
       </c>
       <c r="D54" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp354.000</t>
+          <t>Rp413.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp690.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.337.500</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.120.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>45</v>
       </c>
       <c r="D76" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>90</v>
       </c>
       <c r="D80" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.468.000</t>
+          <t>Rp5.065.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>96</v>
       </c>
       <c r="D85" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp2.439.000</t>
+          <t>Rp3.186.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp8.825.000</t>
+          <t>Rp9.050.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp4.865.000</t>
+          <t>Rp5.045.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>36</v>
       </c>
       <c r="D93" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp993.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.485.000</t>
+          <t>Rp3.705.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.710.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>68</v>
       </c>
       <c r="D97" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.755.000</t>
+          <t>Rp1.305.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.130.000</t>
+          <t>Rp14.312.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp3.656.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.245.000</t>
+          <t>Rp1.835.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.274.000</t>
+          <t>Rp1.624.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.420.000</t>
+          <t>Rp8.790.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp10.250.000</t>
+          <t>Rp9.350.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp8.505.000</t>
+          <t>Rp8.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp385.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp13.790.000</t>
+          <t>Rp14.120.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.148.000</t>
+          <t>Rp7.128.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5180,14 +5180,14 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D55" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp124.000</t>
+          <t>Rp177.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D68" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.110.000</t>
+          <t>Rp11.230.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.200.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.360.000</t>
+          <t>Rp12.760.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp536.000</t>
+          <t>Rp674.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp12.625.000</t>
+          <t>Rp13.150.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.932.000</t>
+          <t>Rp9.432.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp6.914.000</t>
+          <t>Rp7.472.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.717.000</t>
+          <t>Rp5.809.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.071.000</t>
+          <t>Rp2.457.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.639.000</t>
+          <t>Rp6.041.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.540.000</t>
+          <t>Rp6.040.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.300.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>61</v>
       </c>
       <c r="D29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp4.710.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.703.000</t>
+          <t>Rp4.802.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp11.475.000</t>
+          <t>Rp12.525.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.232.000</t>
+          <t>Rp3.520.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp18.760.000</t>
+          <t>Rp19.810.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>112</v>
       </c>
       <c r="D41" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.125.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>112</v>
       </c>
       <c r="D44" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp9.845.000</t>
+          <t>Rp10.395.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D49" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.080.000</t>
+          <t>Rp6.420.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>90</v>
       </c>
       <c r="D51" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.210.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.340.000</t>
+          <t>Rp9.075.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.932.000</t>
+          <t>Rp4.334.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.885.000</t>
+          <t>Rp2.355.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.240.000</t>
+          <t>Rp6.645.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.770.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.455.000</t>
+          <t>Rp5.740.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.299.991</t>
+          <t>Rp3.624.990</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.530.000</t>
+          <t>Rp14.970.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp680.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.260.000</t>
+          <t>Rp3.090.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.699.000</t>
+          <t>Rp2.097.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.474.992</t>
+          <t>Rp4.924.991</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.785.000</t>
+          <t>Rp3.355.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>144</v>
       </c>
       <c r="D37" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.838.000</t>
+          <t>Rp6.083.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.275.000</t>
+          <t>Rp1.460.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.185.000</t>
+          <t>Rp2.284.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp11.364.000</t>
+          <t>Rp11.914.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.730.000</t>
+          <t>Rp2.205.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp775.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>90</v>
       </c>
       <c r="D80" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp5.065.000</t>
+          <t>Rp4.866.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>28</v>
       </c>
       <c r="D92" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp486.000</t>
+          <t>Rp648.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.312.500</t>
+          <t>Rp14.511.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.295.000</t>
+          <t>Rp2.665.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.515.000</t>
+          <t>Rp20.955.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.375.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp30.150.000</t>
+          <t>Rp29.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.491.000</t>
+          <t>Rp4.992.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.200.000</t>
+          <t>Rp8.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.432.000</t>
+          <t>Rp9.531.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.401.000</t>
+          <t>Rp18.637.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.809.000</t>
+          <t>Rp5.993.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.800.000</t>
+          <t>Rp21.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.041.000</t>
+          <t>Rp5.443.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp6.040.000</t>
+          <t>Rp6.540.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.525.000</t>
+          <t>Rp12.475.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.538.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.092.000</t>
+          <t>Rp2.380.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>112</v>
       </c>
       <c r="D41" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.334.000</t>
+          <t>Rp3.736.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.355.000</t>
+          <t>Rp2.905.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp740.000</t>
+          <t>Rp1.110.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.530.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.970.000</t>
+          <t>Rp14.010.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.097.000</t>
+          <t>Rp2.495.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp830.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.409.000</t>
+          <t>Rp4.754.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.284.000</t>
+          <t>Rp2.383.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-08.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-08.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.668.985</t>
+          <t>Rp6.816.985</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.285.000</t>
+          <t>Rp5.410.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp7.650.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp9.050.000</t>
+          <t>Rp8.925.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp648.000</t>
+          <t>Rp729.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.300.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.790.000</t>
+          <t>Rp7.605.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp3.410.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>170</v>
       </c>
       <c r="D28" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp14.120.000</t>
+          <t>Rp14.395.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.345.000</t>
+          <t>Rp2.464.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.755.000</t>
+          <t>Rp15.950.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.300.000</t>
+          <t>Rp21.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.475.000</t>
+          <t>Rp12.875.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D46" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.075.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp9.175.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.645.000</t>
+          <t>Rp6.795.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.924.991</t>
+          <t>Rp5.174.991</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>144</v>
       </c>
       <c r="D37" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.083.000</t>
+          <t>Rp5.885.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
